--- a/results/Int All Data -1.0/Linea_fi_all.xlsx
+++ b/results/Int All Data -1.0/Linea_fi_all.xlsx
@@ -1616,7 +1616,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>-9.168704156479191e-05 +/- 0.000433296053751766</t>
+          <t>-0.00012224938875305958 +/- 0.00043651763010653144</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0.01421149144254279 +/- 0.003329051979769673</t>
+          <t>0.014242053789731045 +/- 0.0033232951635863606</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.0025656148628722788 +/- 0.0017597792683970272</t>
+          <t>-0.002536125036862258 +/- 0.0017154868265702352</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>-0.0001769389560601242 +/- 0.00047915295810297694</t>
+          <t>-0.00014744913005010352 +/- 0.0004800595870274173</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.034181710565256006 +/- 0.0020428819006122916</t>
+          <t>0.03415211601065406 +/- 0.0020124297129328235</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.0009470257472624866 +/- 0.0010977944356905043</t>
+          <t>-0.001006214856466392 +/- 0.0010353865454001531</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.0007090103397341619 +/- 0.0025727079535689803</t>
+          <t>0.0007385524372230834 +/- 0.0026199360481915825</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>0.002723505032563667 +/- 0.0008761781282977287</t>
+          <t>0.0027531083481350136 +/- 0.0008984008825040531</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
